--- a/artfynd/A 46969-2024 artfynd.xlsx
+++ b/artfynd/A 46969-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124467401</v>
+        <v>124467400</v>
       </c>
       <c r="B2" t="n">
         <v>57513</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491862</v>
+        <v>491857</v>
       </c>
       <c r="R2" t="n">
-        <v>7124408</v>
+        <v>7124398</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124467400</v>
+        <v>124467398</v>
       </c>
       <c r="B3" t="n">
         <v>57513</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491857</v>
+        <v>492070</v>
       </c>
       <c r="R3" t="n">
-        <v>7124398</v>
+        <v>7124326</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124467398</v>
+        <v>124467401</v>
       </c>
       <c r="B4" t="n">
         <v>57513</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>492070</v>
+        <v>491862</v>
       </c>
       <c r="R4" t="n">
-        <v>7124326</v>
+        <v>7124408</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 46969-2024 artfynd.xlsx
+++ b/artfynd/A 46969-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124467400</v>
+        <v>124467398</v>
       </c>
       <c r="B2" t="n">
         <v>57513</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491857</v>
+        <v>492070</v>
       </c>
       <c r="R2" t="n">
-        <v>7124398</v>
+        <v>7124326</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124467398</v>
+        <v>124467401</v>
       </c>
       <c r="B3" t="n">
         <v>57513</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492070</v>
+        <v>491862</v>
       </c>
       <c r="R3" t="n">
-        <v>7124326</v>
+        <v>7124408</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124467401</v>
+        <v>124467400</v>
       </c>
       <c r="B4" t="n">
         <v>57513</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491862</v>
+        <v>491857</v>
       </c>
       <c r="R4" t="n">
-        <v>7124408</v>
+        <v>7124398</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 46969-2024 artfynd.xlsx
+++ b/artfynd/A 46969-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124467398</v>
+        <v>124467401</v>
       </c>
       <c r="B2" t="n">
         <v>57513</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>492070</v>
+        <v>491862</v>
       </c>
       <c r="R2" t="n">
-        <v>7124326</v>
+        <v>7124408</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124467401</v>
+        <v>124467400</v>
       </c>
       <c r="B3" t="n">
         <v>57513</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491862</v>
+        <v>491857</v>
       </c>
       <c r="R3" t="n">
-        <v>7124408</v>
+        <v>7124398</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124467400</v>
+        <v>124467398</v>
       </c>
       <c r="B4" t="n">
         <v>57513</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491857</v>
+        <v>492070</v>
       </c>
       <c r="R4" t="n">
-        <v>7124398</v>
+        <v>7124326</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 46969-2024 artfynd.xlsx
+++ b/artfynd/A 46969-2024 artfynd.xlsx
@@ -682,7 +682,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">

--- a/artfynd/A 46969-2024 artfynd.xlsx
+++ b/artfynd/A 46969-2024 artfynd.xlsx
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124467400</v>
+        <v>124467398</v>
       </c>
       <c r="B3" t="n">
         <v>57513</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491857</v>
+        <v>492070</v>
       </c>
       <c r="R3" t="n">
-        <v>7124398</v>
+        <v>7124326</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124467398</v>
+        <v>124467400</v>
       </c>
       <c r="B4" t="n">
         <v>57513</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>492070</v>
+        <v>491857</v>
       </c>
       <c r="R4" t="n">
-        <v>7124326</v>
+        <v>7124398</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 46969-2024 artfynd.xlsx
+++ b/artfynd/A 46969-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124467401</v>
+        <v>124467398</v>
       </c>
       <c r="B2" t="n">
         <v>57513</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491862</v>
+        <v>492070</v>
       </c>
       <c r="R2" t="n">
-        <v>7124408</v>
+        <v>7124326</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124467398</v>
+        <v>124467401</v>
       </c>
       <c r="B3" t="n">
         <v>57513</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492070</v>
+        <v>491862</v>
       </c>
       <c r="R3" t="n">
-        <v>7124326</v>
+        <v>7124408</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 46969-2024 artfynd.xlsx
+++ b/artfynd/A 46969-2024 artfynd.xlsx
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124467401</v>
+        <v>124467400</v>
       </c>
       <c r="B3" t="n">
         <v>57513</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491862</v>
+        <v>491857</v>
       </c>
       <c r="R3" t="n">
-        <v>7124408</v>
+        <v>7124398</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124467400</v>
+        <v>124467401</v>
       </c>
       <c r="B4" t="n">
         <v>57513</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491857</v>
+        <v>491862</v>
       </c>
       <c r="R4" t="n">
-        <v>7124398</v>
+        <v>7124408</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 46969-2024 artfynd.xlsx
+++ b/artfynd/A 46969-2024 artfynd.xlsx
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124467400</v>
+        <v>124467401</v>
       </c>
       <c r="B3" t="n">
         <v>57513</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491857</v>
+        <v>491862</v>
       </c>
       <c r="R3" t="n">
-        <v>7124398</v>
+        <v>7124408</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124467401</v>
+        <v>124467400</v>
       </c>
       <c r="B4" t="n">
         <v>57513</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491862</v>
+        <v>491857</v>
       </c>
       <c r="R4" t="n">
-        <v>7124408</v>
+        <v>7124398</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 46969-2024 artfynd.xlsx
+++ b/artfynd/A 46969-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124467401</v>
+        <v>124467398</v>
       </c>
       <c r="B2" t="n">
         <v>57513</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491862</v>
+        <v>492070</v>
       </c>
       <c r="R2" t="n">
-        <v>7124408</v>
+        <v>7124326</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124467398</v>
+        <v>124467400</v>
       </c>
       <c r="B3" t="n">
         <v>57513</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492070</v>
+        <v>491857</v>
       </c>
       <c r="R3" t="n">
-        <v>7124326</v>
+        <v>7124398</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124467400</v>
+        <v>124467401</v>
       </c>
       <c r="B4" t="n">
         <v>57513</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491857</v>
+        <v>491862</v>
       </c>
       <c r="R4" t="n">
-        <v>7124398</v>
+        <v>7124408</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 46969-2024 artfynd.xlsx
+++ b/artfynd/A 46969-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124467398</v>
+        <v>124467400</v>
       </c>
       <c r="B2" t="n">
         <v>57513</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>492070</v>
+        <v>491857</v>
       </c>
       <c r="R2" t="n">
-        <v>7124326</v>
+        <v>7124398</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124467400</v>
+        <v>124467398</v>
       </c>
       <c r="B3" t="n">
         <v>57513</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491857</v>
+        <v>492070</v>
       </c>
       <c r="R3" t="n">
-        <v>7124398</v>
+        <v>7124326</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 46969-2024 artfynd.xlsx
+++ b/artfynd/A 46969-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124467400</v>
+        <v>124467401</v>
       </c>
       <c r="B2" t="n">
         <v>57513</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491857</v>
+        <v>491862</v>
       </c>
       <c r="R2" t="n">
-        <v>7124398</v>
+        <v>7124408</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124467401</v>
+        <v>124467400</v>
       </c>
       <c r="B4" t="n">
         <v>57513</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491862</v>
+        <v>491857</v>
       </c>
       <c r="R4" t="n">
-        <v>7124408</v>
+        <v>7124398</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 46969-2024 artfynd.xlsx
+++ b/artfynd/A 46969-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124467401</v>
+        <v>124467400</v>
       </c>
       <c r="B2" t="n">
         <v>57513</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491862</v>
+        <v>491857</v>
       </c>
       <c r="R2" t="n">
-        <v>7124408</v>
+        <v>7124398</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124467400</v>
+        <v>124467401</v>
       </c>
       <c r="B4" t="n">
         <v>57513</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491857</v>
+        <v>491862</v>
       </c>
       <c r="R4" t="n">
-        <v>7124398</v>
+        <v>7124408</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 46969-2024 artfynd.xlsx
+++ b/artfynd/A 46969-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124467400</v>
+        <v>124467401</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491857</v>
+        <v>491862</v>
       </c>
       <c r="R2" t="n">
-        <v>7124398</v>
+        <v>7124408</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124467398</v>
+        <v>124467400</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492070</v>
+        <v>491857</v>
       </c>
       <c r="R3" t="n">
-        <v>7124326</v>
+        <v>7124398</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124467401</v>
+        <v>124467398</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491862</v>
+        <v>492070</v>
       </c>
       <c r="R4" t="n">
-        <v>7124408</v>
+        <v>7124326</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 46969-2024 artfynd.xlsx
+++ b/artfynd/A 46969-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124467401</v>
+        <v>124467398</v>
       </c>
       <c r="B2" t="n">
-        <v>57635</v>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491862</v>
+        <v>492070</v>
       </c>
       <c r="R2" t="n">
-        <v>7124408</v>
+        <v>7124326</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,7 +780,7 @@
         <v>124467400</v>
       </c>
       <c r="B3" t="n">
-        <v>57635</v>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124467398</v>
+        <v>124467401</v>
       </c>
       <c r="B4" t="n">
-        <v>57635</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>492070</v>
+        <v>491862</v>
       </c>
       <c r="R4" t="n">
-        <v>7124326</v>
+        <v>7124408</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 46969-2024 artfynd.xlsx
+++ b/artfynd/A 46969-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124467398</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124467400</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,8 +993,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124467401</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 46969-2024 artfynd.xlsx
+++ b/artfynd/A 46969-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124467398</v>
+        <v>136300004</v>
       </c>
       <c r="B2" t="n">
-        <v>57953</v>
+        <v>92069</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kvisselnvattnet, Jmt</t>
+          <t>Åkroken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>492070</v>
+        <v>491875</v>
       </c>
       <c r="R2" t="n">
-        <v>7124326</v>
+        <v>7124311</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,17 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -767,27 +772,42 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Isak Vahlström, Carl Jansson, Irena Koelemeijer, Maja Östlund, Noel Wieser</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124467398</t>
+          <t>https://artportalen.se/Sighting/136300004</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124467400</v>
+        <v>124467398</v>
       </c>
       <c r="B3" t="n">
         <v>57953</v>
@@ -822,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491857</v>
+        <v>492070</v>
       </c>
       <c r="R3" t="n">
-        <v>7124398</v>
+        <v>7124326</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,13 +908,13 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124467400</t>
+          <t>https://artportalen.se/Sighting/124467398</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124467401</v>
+        <v>124467400</v>
       </c>
       <c r="B4" t="n">
         <v>57953</v>
@@ -929,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491862</v>
+        <v>491857</v>
       </c>
       <c r="R4" t="n">
-        <v>7124408</v>
+        <v>7124398</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,6 +1014,113 @@
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124467400</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>124467401</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kvisselnvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>491862</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7124408</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/124467401</t>
         </is>
@@ -1004,6 +1131,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 46969-2024 artfynd.xlsx
+++ b/artfynd/A 46969-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136300004</v>
       </c>
       <c r="B2" t="n">
-        <v>92069</v>
+        <v>92070</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Carl Jansson, Irena Koelemeijer, Maja Östlund, Noel Wieser</t>
+          <t>Noel Wieser, Maja Östlund, Irena Koelemeijer, Carl Jansson, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 46969-2024 artfynd.xlsx
+++ b/artfynd/A 46969-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136300004</v>
       </c>
       <c r="B2" t="n">
-        <v>92070</v>
+        <v>92076</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Noel Wieser, Maja Östlund, Irena Koelemeijer, Carl Jansson, Isak Vahlström</t>
+          <t>Isak Vahlström, Carl Jansson, Irena Koelemeijer, Maja Östlund, Noel Wieser</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 46969-2024 artfynd.xlsx
+++ b/artfynd/A 46969-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136300004</v>
       </c>
       <c r="B2" t="n">
-        <v>92076</v>
+        <v>92083</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Carl Jansson, Irena Koelemeijer, Maja Östlund, Noel Wieser</t>
+          <t>Noel Wieser, Maja Östlund, Irena Koelemeijer, Carl Jansson, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 46969-2024 artfynd.xlsx
+++ b/artfynd/A 46969-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Noel Wieser, Maja Östlund, Irena Koelemeijer, Carl Jansson, Isak Vahlström</t>
+          <t>Isak Vahlström, Carl Jansson, Irena Koelemeijer, Maja Östlund, Noel Wieser</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 46969-2024 artfynd.xlsx
+++ b/artfynd/A 46969-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136300004</v>
       </c>
       <c r="B2" t="n">
-        <v>92083</v>
+        <v>92084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 46969-2024 artfynd.xlsx
+++ b/artfynd/A 46969-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136300004</v>
       </c>
       <c r="B2" t="n">
-        <v>92084</v>
+        <v>92097</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Carl Jansson, Irena Koelemeijer, Maja Östlund, Noel Wieser</t>
+          <t>Noel Wieser, Maja Östlund, Irena Koelemeijer, Carl Jansson, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 46969-2024 artfynd.xlsx
+++ b/artfynd/A 46969-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136300004</v>
       </c>
       <c r="B2" t="n">
-        <v>92097</v>
+        <v>92098</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
